--- a/IaR_GaR_April_2026/Outputs/wis/wis_skewt_gdp.xlsx
+++ b/IaR_GaR_April_2026/Outputs/wis/wis_skewt_gdp.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="38" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="5">
   <si>
     <t>Specification</t>
   </si>
@@ -103,7 +103,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.90625" customWidth="true"/>
@@ -262,6 +262,30 @@
         <v>1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>1</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>5</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>9</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>